--- a/k_variation_report.xlsx
+++ b/k_variation_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,19 +424,19 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>hit_rate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mrr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>avg_time_s</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>min_time_s</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>max_time_s</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>avg_docs_found</t>
@@ -453,11 +453,6 @@
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>answer_rate_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>context_mode</t>
         </is>
@@ -468,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.302</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.898</v>
+        <v>0.7</v>
       </c>
       <c r="D2" t="n">
-        <v>16.648</v>
+        <v>3.364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -485,12 +480,9 @@
       <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Direct Context</t>
         </is>
       </c>
     </row>
@@ -499,16 +491,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.919</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>1.021</v>
+        <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2.291</v>
+        <v>3.541</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -516,12 +508,9 @@
       <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Direct Context</t>
         </is>
       </c>
     </row>
@@ -530,16 +519,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.313</v>
+        <v>0.8</v>
       </c>
       <c r="C4" t="n">
-        <v>1.068</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>4.007</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -547,12 +536,9 @@
       <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Direct Context</t>
         </is>
       </c>
     </row>
@@ -561,16 +547,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3.642</v>
+        <v>0.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4.651</v>
+        <v>8.859</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -578,12 +564,9 @@
       <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Direct Context</t>
         </is>
       </c>
     </row>
@@ -592,16 +575,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3.711</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.924</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>5.493</v>
+        <v>6.761</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -609,12 +592,9 @@
       <c r="G6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Direct Context</t>
         </is>
       </c>
     </row>
@@ -623,16 +603,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.088</v>
+        <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.956</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>2.99</v>
+        <v>16.296</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -640,12 +620,9 @@
       <c r="G7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Map-Reduce</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Map-Reduce Async</t>
         </is>
       </c>
     </row>
@@ -654,16 +631,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2.194</v>
+        <v>0.9</v>
       </c>
       <c r="C8" t="n">
-        <v>0.93</v>
+        <v>0.764</v>
       </c>
       <c r="D8" t="n">
-        <v>2.966</v>
+        <v>14.843</v>
       </c>
       <c r="E8" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -671,12 +648,9 @@
       <c r="G8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Map-Reduce</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Map-Reduce Async</t>
         </is>
       </c>
     </row>
@@ -685,16 +659,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2.838</v>
+        <v>0.9</v>
       </c>
       <c r="C9" t="n">
-        <v>0.923</v>
+        <v>0.764</v>
       </c>
       <c r="D9" t="n">
-        <v>5.852</v>
+        <v>26.926</v>
       </c>
       <c r="E9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -702,12 +676,9 @@
       <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Map-Reduce</t>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Map-Reduce Async</t>
         </is>
       </c>
     </row>
@@ -716,16 +687,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>5.201</v>
+        <v>0.9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.916</v>
+        <v>0.764</v>
       </c>
       <c r="D10" t="n">
-        <v>9.771000000000001</v>
+        <v>20.285</v>
       </c>
       <c r="E10" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
@@ -733,12 +704,9 @@
       <c r="G10" t="n">
         <v>10</v>
       </c>
-      <c r="H10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Map-Reduce</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Map-Reduce Async</t>
         </is>
       </c>
     </row>
@@ -747,16 +715,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4.799</v>
+        <v>0.9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.886</v>
+        <v>0.764</v>
       </c>
       <c r="D11" t="n">
-        <v>9.904999999999999</v>
+        <v>16.318</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -764,12 +732,9 @@
       <c r="G11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Map-Reduce</t>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Map-Reduce Async</t>
         </is>
       </c>
     </row>
